--- a/output/pdf_financials_xlsx/GMX.xlsx
+++ b/output/pdf_financials_xlsx/GMX.xlsx
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.037341</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.025928</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.016845</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.018259</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.019064</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1904,19 +1904,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.314329</v>
+        <v>-2.35167</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.720489</v>
+        <v>0.694561</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.614043</v>
+        <v>2.597198</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.319185</v>
+        <v>-1.337444</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.342113</v>
+        <v>-5.361177</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-2.417033</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.262629</v>
+        <v>-2.29997</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.769316</v>
+        <v>0.743388</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.664095</v>
+        <v>2.64725</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.252124</v>
+        <v>-1.270383</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.283147</v>
+        <v>-5.302211</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-2.357476</v>
@@ -2069,19 +2069,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-361.070879159459</v>
+        <v>-367.0297649063903</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>20.4979024258322</v>
+        <v>19.80706847190823</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>301.1454195651633</v>
+        <v>299.2412852934593</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-166.9033562647209</v>
+        <v>-169.3372113637666</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-398.2351655309654</v>
+        <v>-399.6721793402883</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-203.1714896866258</v>
@@ -63010,7 +63010,7 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E588" s="5" t="n">

--- a/output/pdf_financials_xlsx/GMX.xlsx
+++ b/output/pdf_financials_xlsx/GMX.xlsx
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.000443</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -50468,7 +50468,11 @@
           <t>Proceeds on disposal of properties, plant and equipment</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E454" s="5" t="n">
         <v>0.000443</v>
       </c>
